--- a/output/pdf_financials_xlsx/SAM.xlsx
+++ b/output/pdf_financials_xlsx/SAM.xlsx
@@ -6119,31 +6119,31 @@
         <v>-2.188</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>-2.97</v>
+        <v>-3.171</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-3.24</v>
+        <v>-3.424</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-3.294</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-2.542</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.915</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>5.065</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>5.386</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>5.209</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>1.234</v>
       </c>
       <c r="L91" s="1" t="inlineStr">
         <is>
@@ -6161,16 +6161,16 @@
         </is>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>2.185</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>3.794</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>4.131</v>
       </c>
     </row>
     <row r="92">
@@ -7843,7 +7843,7 @@
         <v>-0.822</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-1.603</v>
       </c>
     </row>
     <row r="119">
@@ -11220,7 +11220,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -16009,7 +16013,11 @@
           <t>Foreign Currency Translation Reserve</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -25449,7 +25457,11 @@
           <t>Exploration and evaluation asset expenditures (note 10)</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SAM.xlsx
+++ b/output/pdf_financials_xlsx/SAM.xlsx
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1968,10 +1968,10 @@
         <v>109.625</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>74.56</v>
+        <v>74.48531</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>83.54000000000001</v>
+        <v>88.01603299999999</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>143.35</v>
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6.932</v>
+        <v>6.586</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.08</v>
+        <v>-4.084</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.662</v>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9.337</v>
+        <v>8.991</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.963</v>
+        <v>-1.967</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0.6820000000000001</v>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>35.15966259978913</v>
+        <v>33.85675553547221</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-8.460842205077368</v>
+        <v>-8.478082841256843</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>1.728113518307361</v>
@@ -2428,28 +2428,28 @@
         <v>0.824</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.712</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.675</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.638</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>5.454</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>4.248</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>5.558</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.321</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2556,28 +2556,28 @@
         <v>1.585</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.25</v>
+        <v>1.962</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.612</v>
+        <v>3.287</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2.71</v>
+        <v>8.348000000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4.324</v>
+        <v>9.778</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.615</v>
+        <v>5.985</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>5.742</v>
+        <v>9.99</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>4.005</v>
+        <v>9.563000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.321</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -3324,28 +3324,28 @@
         <v>0.832</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.305</v>
+        <v>1.593</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.26</v>
+        <v>2.585</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8.063000000000001</v>
+        <v>2.425</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>6.345</v>
+        <v>0.891</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.933</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.439</v>
+        <v>0.191</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.907</v>
+        <v>0.349</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.676</v>
+        <v>0.355</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -8218,16 +8218,16 @@
         </is>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.611</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.599</v>
       </c>
     </row>
     <row r="125">
@@ -8282,16 +8282,16 @@
         </is>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.611</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.599</v>
       </c>
     </row>
     <row r="126">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -15130,7 +15130,11 @@
           <t>Reclamation Deposits</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -17532,7 +17536,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -19310,7 +19318,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -25259,7 +25267,11 @@
           <t>Lease payments (note 11)</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -27755,7 +27767,11 @@
           <t>Lease payments (note 12)</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -29347,7 +29363,11 @@
           <t>Cash received from reclamation deposit</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -35372,7 +35392,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -70077,7 +70101,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E616" s="5" t="n">
@@ -71291,7 +71315,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -73103,7 +73127,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E646" s="5" t="n">
@@ -73206,7 +73230,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E647" s="5" t="n">
